--- a/results/result_evaluation_logs/Z_GenIE_base_sc.xlsx
+++ b/results/result_evaluation_logs/Z_GenIE_base_sc.xlsx
@@ -817,10 +817,10 @@
         <v>1</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
         <v>1</v>
@@ -1194,10 +1194,10 @@
         <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
@@ -1877,10 +1877,10 @@
         <v>2</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
         <v>3</v>
@@ -2864,10 +2864,10 @@
         <v>2</v>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -2940,10 +2940,10 @@
         <v>4</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
         <v>3</v>
